--- a/9_筆記/閱讀數據.xlsx
+++ b/9_筆記/閱讀數據.xlsx
@@ -2417,11 +2417,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="10641576"/>
-        <c:axId val="13117452"/>
+        <c:axId val="15470789"/>
+        <c:axId val="85052244"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="10641576"/>
+        <c:axId val="15470789"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2497,12 +2497,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13117452"/>
+        <c:crossAx val="85052244"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="13117452"/>
+        <c:axId val="85052244"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,7 +2578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10641576"/>
+        <c:crossAx val="15470789"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2617,9 +2617,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>642960</xdr:colOff>
+      <xdr:colOff>642600</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>201600</xdr:rowOff>
+      <xdr:rowOff>201240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2628,7 +2628,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7869960" y="2651760"/>
-        <a:ext cx="4549680" cy="2734560"/>
+        <a:ext cx="4549320" cy="2734200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2818,7 +2818,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R144"/>
+  <dimension ref="A1:R145"/>
   <sheetFormatPr defaultColWidth="8.64453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.73"/>
@@ -2933,19 +2933,19 @@
       </c>
       <c r="O2" s="1" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>811.72027972028</v>
+        <v>816</v>
       </c>
       <c r="P2" s="2" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44830.7202797203</v>
+        <v>44835</v>
       </c>
       <c r="Q2" s="1" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>1664.24609118769</v>
+        <v>1750.78339657351</v>
       </c>
       <c r="R2" s="2" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>45683.2460911877</v>
+        <v>45769.7833965735</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,19 +2996,19 @@
       </c>
       <c r="O3" s="1" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>931.090909090909</v>
+        <v>936</v>
       </c>
       <c r="P3" s="2" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44950.0909090909</v>
+        <v>44955</v>
       </c>
       <c r="Q3" s="1" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>1824.52661361347</v>
+        <v>1919.39816991927</v>
       </c>
       <c r="R3" s="2" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>45843.5266136135</v>
+        <v>45938.3981699193</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="O4" s="1" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1408.57342657343</v>
+        <v>1416</v>
       </c>
       <c r="P4" s="2" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45427.5734265734</v>
+        <v>45435</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>2198.51449927362</v>
+        <v>2312.83264105939</v>
       </c>
       <c r="R4" s="2" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>46217.5144992736</v>
+        <v>46331.8326410594</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="O5" s="1" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>2100.92307692308</v>
+        <v>2112</v>
       </c>
       <c r="P5" s="2" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>46119.9230769231</v>
+        <v>46131</v>
       </c>
       <c r="Q5" s="1" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>2649.97130410624</v>
+        <v>2787.76425264995</v>
       </c>
       <c r="R5" s="2" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>46668.9713041062</v>
+        <v>46806.76425265</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,19 +3185,19 @@
       </c>
       <c r="O6" s="1" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>3163.32167832168</v>
+        <v>3180</v>
       </c>
       <c r="P6" s="2" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>47182.3216783217</v>
+        <v>47199</v>
       </c>
       <c r="Q6" s="1" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>3499.45807296288</v>
+        <v>3681.4225513825</v>
       </c>
       <c r="R6" s="2" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>47518.4580729629</v>
+        <v>47700.4225513825</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="O7" s="1" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>3509.4965034965</v>
+        <v>3528</v>
       </c>
       <c r="P7" s="2" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>47528.4965034965</v>
+        <v>47547</v>
       </c>
       <c r="Q7" s="1" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>3638.36785906522</v>
+        <v>3827.55535494882</v>
       </c>
       <c r="R7" s="2" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>47657.3678590652</v>
+        <v>47846.5553549488</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="O8" s="1" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>3509.4965034965</v>
+        <v>3528</v>
       </c>
       <c r="P8" s="2" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>47528.4965034965</v>
+        <v>47547</v>
       </c>
       <c r="Q8" s="1" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>3638.36785906522</v>
+        <v>3827.55535494882</v>
       </c>
       <c r="R8" s="2" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>47657.3678590652</v>
+        <v>47846.5553549488</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>11.9370629370629</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>2.67134204042968</v>
+        <v>2.81024622242939</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8021,6 +8021,40 @@
       <c r="I144" s="1" t="n">
         <f aca="false">E144/H144</f>
         <v>13</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B145" s="1" t="str">
+        <f aca="false">"卷"&amp;ROW(B144)</f>
+        <v>卷144</v>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E145" s="1" t="n">
+        <f aca="false">D145-C145+1</f>
+        <v>21</v>
+      </c>
+      <c r="F145" s="1" t="n">
+        <f aca="false">G144+1</f>
+        <v>501</v>
+      </c>
+      <c r="G145" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H145" s="1" t="n">
+        <f aca="false">IF(F145*G145&lt;0,ABS(F145)+ABS(G145),G145-F145+1)</f>
+        <v>1</v>
+      </c>
+      <c r="I145" s="1" t="n">
+        <f aca="false">E145/H145</f>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -12112,7 +12146,7 @@
         <v>1008|[卷142](9_筆記/资治通鉴142.html)|齊紀八|499|499|</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="n">
         <v>1009</v>
       </c>
@@ -12140,24 +12174,24 @@
       <c r="A145" s="1" t="n">
         <v>1010</v>
       </c>
-      <c r="B145" s="1" t="e">
+      <c r="B145" s="1" t="str">
         <f aca="false">VLOOKUP($A145,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷144</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="D145" s="1" t="e">
+      <c r="D145" s="1" t="n">
         <f aca="false">VLOOKUP($A145,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E145" s="1" t="e">
+        <v>501</v>
+      </c>
+      <c r="E145" s="1" t="n">
         <f aca="false">VLOOKUP($A145,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I145" s="1" t="e">
+        <v>501</v>
+      </c>
+      <c r="I145" s="1" t="str">
         <f aca="false">A145&amp;"|"&amp;"["&amp;B145&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B145,"卷","")&amp;".html)|"&amp;C145&amp;"|"&amp;D145&amp;"|"&amp;E145&amp;"|"&amp;H145</f>
-        <v>#N/A</v>
+        <v>1010|[卷144](9_筆記/资治通鉴144.html)|齊紀十|501|501|</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/9_筆記/閱讀數據.xlsx
+++ b/9_筆記/閱讀數據.xlsx
@@ -2417,11 +2417,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="15470789"/>
-        <c:axId val="85052244"/>
+        <c:axId val="38265343"/>
+        <c:axId val="63571191"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="15470789"/>
+        <c:axId val="38265343"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2497,12 +2497,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85052244"/>
+        <c:crossAx val="63571191"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="85052244"/>
+        <c:axId val="63571191"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,7 +2578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15470789"/>
+        <c:crossAx val="38265343"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2617,9 +2617,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>642600</xdr:colOff>
+      <xdr:colOff>642240</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>201240</xdr:rowOff>
+      <xdr:rowOff>200880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2628,7 +2628,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="7869960" y="2651760"/>
-        <a:ext cx="4549320" cy="2734200"/>
+        <a:ext cx="4548960" cy="2733840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2818,7 +2818,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R145"/>
+  <dimension ref="A1:R146"/>
   <sheetFormatPr defaultColWidth="8.64453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.73"/>
@@ -2933,19 +2933,19 @@
       </c>
       <c r="O2" s="1" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>816</v>
+        <v>823.972413793103</v>
       </c>
       <c r="P2" s="2" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44835</v>
+        <v>44842.9724137931</v>
       </c>
       <c r="Q2" s="1" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>1750.78339657351</v>
+        <v>1772.68807188339</v>
       </c>
       <c r="R2" s="2" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>45769.7833965735</v>
+        <v>45791.6880718834</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,19 +2996,19 @@
       </c>
       <c r="O3" s="1" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>936</v>
+        <v>945.144827586207</v>
       </c>
       <c r="P3" s="2" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44955</v>
+        <v>44964.1448275862</v>
       </c>
       <c r="Q3" s="1" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>1919.39816991927</v>
+        <v>1943.41244477746</v>
       </c>
       <c r="R3" s="2" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>45938.3981699193</v>
+        <v>45962.4124447775</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3059,19 +3059,19 @@
       </c>
       <c r="O4" s="1" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1416</v>
+        <v>1429.83448275862</v>
       </c>
       <c r="P4" s="2" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45435</v>
+        <v>45448.8344827586</v>
       </c>
       <c r="Q4" s="1" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>2312.83264105939</v>
+        <v>2341.76931486361</v>
       </c>
       <c r="R4" s="2" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>46331.8326410594</v>
+        <v>46360.7693148636</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="O5" s="1" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>2112</v>
+        <v>2132.63448275862</v>
       </c>
       <c r="P5" s="2" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>46131</v>
+        <v>46151.6344827586</v>
       </c>
       <c r="Q5" s="1" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>2787.76425264995</v>
+        <v>2822.6429651819</v>
       </c>
       <c r="R5" s="2" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>46806.76425265</v>
+        <v>46841.6429651819</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,19 +3185,19 @@
       </c>
       <c r="O6" s="1" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>3180</v>
+        <v>3211.06896551724</v>
       </c>
       <c r="P6" s="2" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>47199</v>
+        <v>47230.0689655172</v>
       </c>
       <c r="Q6" s="1" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>3681.4225513825</v>
+        <v>3727.48214152045</v>
       </c>
       <c r="R6" s="2" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>47700.4225513825</v>
+        <v>47746.4821415205</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="O7" s="1" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>3528</v>
+        <v>3562.46896551724</v>
       </c>
       <c r="P7" s="2" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>47547</v>
+        <v>47581.4689655172</v>
       </c>
       <c r="Q7" s="1" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>3827.55535494882</v>
+        <v>3875.44326469531</v>
       </c>
       <c r="R7" s="2" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>47846.5553549488</v>
+        <v>47894.4432646953</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="O8" s="1" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>3528</v>
+        <v>3562.46896551724</v>
       </c>
       <c r="P8" s="2" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>47547</v>
+        <v>47581.4689655172</v>
       </c>
       <c r="Q8" s="1" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>3827.55535494882</v>
+        <v>3875.44326469531</v>
       </c>
       <c r="R8" s="2" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>47846.5553549488</v>
+        <v>47894.4432646953</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>12</v>
+        <v>12.1172413793103</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>2.81024622242939</v>
+        <v>2.84540621490111</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8055,6 +8055,40 @@
       <c r="I145" s="1" t="n">
         <f aca="false">E145/H145</f>
         <v>21</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B146" s="1" t="str">
+        <f aca="false">"卷"&amp;ROW(B145)</f>
+        <v>卷145</v>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="E146" s="1" t="n">
+        <f aca="false">D146-C146+1</f>
+        <v>29</v>
+      </c>
+      <c r="F146" s="1" t="n">
+        <f aca="false">G145+1</f>
+        <v>502</v>
+      </c>
+      <c r="G146" s="1" t="n">
+        <v>504</v>
+      </c>
+      <c r="H146" s="1" t="n">
+        <f aca="false">IF(F146*G146&lt;0,ABS(F146)+ABS(G146),G146-F146+1)</f>
+        <v>3</v>
+      </c>
+      <c r="I146" s="1" t="n">
+        <f aca="false">E146/H146</f>
+        <v>9.66666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -12170,7 +12204,7 @@
         <v>1009|[卷143](9_筆記/资治通鉴143.html)|齊紀九|500|500|</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="n">
         <v>1010</v>
       </c>
@@ -12198,24 +12232,24 @@
       <c r="A146" s="1" t="n">
         <v>1101</v>
       </c>
-      <c r="B146" s="1" t="e">
+      <c r="B146" s="1" t="str">
         <f aca="false">VLOOKUP($A146,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷145</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D146" s="1" t="e">
+      <c r="D146" s="1" t="n">
         <f aca="false">VLOOKUP($A146,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E146" s="1" t="e">
+        <v>502</v>
+      </c>
+      <c r="E146" s="1" t="n">
         <f aca="false">VLOOKUP($A146,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I146" s="1" t="e">
+        <v>504</v>
+      </c>
+      <c r="I146" s="1" t="str">
         <f aca="false">A146&amp;"|"&amp;"["&amp;B146&amp;"](9_筆記/资治通鉴"&amp;SUBSTITUTE(B146,"卷","")&amp;".html)|"&amp;C146&amp;"|"&amp;D146&amp;"|"&amp;E146&amp;"|"&amp;H146</f>
-        <v>#N/A</v>
+        <v>1101|[卷145](9_筆記/资治通鉴145.html)|梁紀一|502|504|</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
